--- a/data-manipulation-scripts/sheets-cleanup/sheets/LUBRIFICANTE ANTIFERRUGEM 15_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/LUBRIFICANTE ANTIFERRUGEM 15_02.xlsx
@@ -337,7 +337,9 @@
       <c r="C2" s="2">
         <v>10.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>22.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
